--- a/data/trans_orig/IQ23_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58111</t>
+          <t>58377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71879</t>
+          <t>72132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>49401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62533</t>
+          <t>62720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112231</t>
+          <t>111929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132457</t>
+          <t>131314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31535</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42676</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>63204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>286694</t>
+          <t>285001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314408</t>
+          <t>313706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>345514</t>
+          <t>345117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>375499</t>
+          <t>374526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642759</t>
+          <t>642665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>683501</t>
+          <t>682975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98699</t>
+          <t>99401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126413</t>
+          <t>128106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100806</t>
+          <t>101779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130791</t>
+          <t>131188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205911</t>
+          <t>206437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>246653</t>
+          <t>246747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121189</t>
+          <t>120866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139651</t>
+          <t>139157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105411</t>
+          <t>105173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122647</t>
+          <t>122785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233428</t>
+          <t>231403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258776</t>
+          <t>256873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32737</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51199</t>
+          <t>51522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34313</t>
+          <t>34175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51549</t>
+          <t>51787</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70572</t>
+          <t>72475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95920</t>
+          <t>97945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>513045</t>
+          <t>512705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>549094</t>
+          <t>550480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1000496</t>
+          <t>1004034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1054812</t>
+          <t>1054463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160760</t>
+          <t>159460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197674</t>
+          <t>196315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169658</t>
+          <t>168272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205707</t>
+          <t>206047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>339081</t>
+          <t>339430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393397</t>
+          <t>389859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>56387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71088</t>
+          <t>71000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>51395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111409</t>
+          <t>112576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132409</t>
+          <t>132923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35995</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67152</t>
+          <t>65985</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>306248</t>
+          <t>309275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>339943</t>
+          <t>340757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>339554</t>
+          <t>341092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>372594</t>
+          <t>373359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>659497</t>
+          <t>658789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>702580</t>
+          <t>706023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111592</t>
+          <t>110778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145287</t>
+          <t>142260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121852</t>
+          <t>121087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154892</t>
+          <t>153354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243400</t>
+          <t>239957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286483</t>
+          <t>287191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111792</t>
+          <t>112586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131047</t>
+          <t>132310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111781</t>
+          <t>111540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131159</t>
+          <t>130618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231018</t>
+          <t>229808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257533</t>
+          <t>256882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34979</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>53440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>40274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>59352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>80036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>107110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>515624</t>
+          <t>517416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>558156</t>
+          <t>557587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1018699</t>
+          <t>1017388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1075360</t>
+          <t>1076158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180573</t>
+          <t>178446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219761</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193374</t>
+          <t>193943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>235906</t>
+          <t>234114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386099</t>
+          <t>385301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442760</t>
+          <t>444071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>36693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>47524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36237</t>
+          <t>36423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49100</t>
+          <t>49808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76207</t>
+          <t>76457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94006</t>
+          <t>94548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33222</t>
+          <t>32680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51021</t>
+          <t>50771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>316306</t>
+          <t>316268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>349905</t>
+          <t>346305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>309484</t>
+          <t>307511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>341481</t>
+          <t>342376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>637530</t>
+          <t>636104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>681878</t>
+          <t>682300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120039</t>
+          <t>123639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153638</t>
+          <t>153676</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142592</t>
+          <t>141697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174589</t>
+          <t>176562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272139</t>
+          <t>271717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316487</t>
+          <t>317913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94068</t>
+          <t>95286</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115755</t>
+          <t>116252</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114552</t>
+          <t>113822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134880</t>
+          <t>135137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215628</t>
+          <t>216512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245217</t>
+          <t>246111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54176</t>
+          <t>53679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75863</t>
+          <t>74645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51439</t>
+          <t>51182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71767</t>
+          <t>72497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111033</t>
+          <t>110139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140622</t>
+          <t>139738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198807</t>
+          <t>201633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237807</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223042</t>
+          <t>222887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>264160</t>
+          <t>265549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438240</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>497617</t>
+          <t>491817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>31586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>45320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>63211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84014</t>
+          <t>84820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>30418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31292</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52600</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>308261</t>
+          <t>308559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>356542</t>
+          <t>355661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>330276</t>
+          <t>330843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>373329</t>
+          <t>372823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>649775</t>
+          <t>648742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>708687</t>
+          <t>713674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100652</t>
+          <t>101533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148933</t>
+          <t>148635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141293</t>
+          <t>141799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184346</t>
+          <t>183779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>263130</t>
+          <t>258143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322042</t>
+          <t>323075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99060</t>
+          <t>99006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116267</t>
+          <t>115745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127587</t>
+          <t>127288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147843</t>
+          <t>147970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231334</t>
+          <t>232299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258359</t>
+          <t>258396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48685</t>
+          <t>48739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35506</t>
+          <t>35379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55762</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72735</t>
+          <t>72698</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99760</t>
+          <t>98795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>446675</t>
+          <t>447342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>496221</t>
+          <t>496429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>962550</t>
+          <t>965413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1035668</t>
+          <t>1033705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162021</t>
+          <t>161813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211567</t>
+          <t>210900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207922</t>
+          <t>205343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256574</t>
+          <t>255758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382549</t>
+          <t>384512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>455667</t>
+          <t>452804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48134</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61808</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65400</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58377</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>72132</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>58168</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71469</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>72,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>55996</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>49401</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>62720</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111929</t>
+          <t>111100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131314</t>
+          <t>131592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29491</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23679</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37353</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24246</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17514</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31269</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18177</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31478</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>29491</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22767</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36086</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43819</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63204</t>
+          <t>64033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85487</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85487</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85487</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>89646</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>89646</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>89646</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85487</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85487</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85487</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>361778</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>347730</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>375904</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>75,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>301024</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>285001</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>313706</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>283963</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>314547</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>361778</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>345117</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>374526</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>75,96%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642665</t>
+          <t>642103</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682975</t>
+          <t>682612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -1184,67 +1184,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>114527</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100401</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>128575</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>112083</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99401</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>128106</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98560</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>129144</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>114527</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>101779</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>131188</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>24,04%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206437</t>
+          <t>206800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>246747</t>
+          <t>247309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476305</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476305</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476305</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>413107</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>413107</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>413107</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476305</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476305</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>114594</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>105205</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>123238</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>130748</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>120866</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>139157</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>138733</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>114594</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>105173</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>122785</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,01%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231403</t>
+          <t>229909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256873</t>
+          <t>257592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42366</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33722</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51755</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>41640</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>33231</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51522</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>33655</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>52085</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>24,15%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>42366</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>34175</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51787</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>71756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97945</t>
+          <t>99439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156960</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156960</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156960</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172388</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172388</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172388</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156960</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156960</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156960</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,74 +1752,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>532367</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>512900</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>550520</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>478826</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>515681</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>480522</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>515664</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>76,38%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>532367</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>512705</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>550480</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>74,07%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>71,33%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1535</t>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1004034</t>
+          <t>1004191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1054463</t>
+          <t>1058095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>186385</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168232</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205852</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>177969</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159460</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>196315</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>159477</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>194619</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>23,62%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>186385</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168272</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206047</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>339430</t>
+          <t>335798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>389859</t>
+          <t>389702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>718752</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>718752</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>718752</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1009</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>675141</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>718752</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>718752</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>718752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59010</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52176</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66387</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>63826</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>56387</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71000</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>56414</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>70459</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>69,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>59010</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51395</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66081</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112576</t>
+          <t>111705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132923</t>
+          <t>133133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19805</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34016</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28543</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21369</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35982</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21910</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35955</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>30,9%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27182</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65985</t>
+          <t>66856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>357298</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>341005</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>373386</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>466</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>324323</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>309275</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>340757</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>309324</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>338190</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>71,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>357298</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>341092</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>373359</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>658789</t>
+          <t>659322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>702276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>137148</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>121060</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>153441</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>127212</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>110778</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142260</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>113345</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>142211</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>28,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>137148</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>121087</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>153354</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>239957</t>
+          <t>243704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>287191</t>
+          <t>286658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>451535</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>451535</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>451535</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121006</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110580</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>130396</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>122802</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>112586</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>132310</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>113749</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>132042</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>73,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>121006</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>111540</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>130618</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,81%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229808</t>
+          <t>231315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256882</t>
+          <t>256956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49886</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40496</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60312</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>43224</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>53440</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>33984</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>52277</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>26,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>49886</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>40274</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>59352</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80036</t>
+          <t>79962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107110</t>
+          <t>105603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>170892</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>170892</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>170892</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>170892</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>170892</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>170892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>537314</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>517554</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>556219</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>491483</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>531483</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>490900</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>528676</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>537314</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>517416</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>557587</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1017388</t>
+          <t>1016741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1076158</t>
+          <t>1075236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>214216</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>195311</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>233976</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>198978</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>178446</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>218446</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>181253</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>219029</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>214216</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>193943</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>234114</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>385301</t>
+          <t>386223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>444071</t>
+          <t>444718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>751530</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>751530</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>751530</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>709929</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>751530</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>751530</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>751530</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43023</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36184</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49250</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>42630</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36693</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47524</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36805</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>47404</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43023</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36423</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>49808</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>63,41%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76457</t>
+          <t>76827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94548</t>
+          <t>94232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24827</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18600</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31666</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16748</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11854</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11974</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22573</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24827</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18042</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31427</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,59%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50771</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67850</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67850</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67850</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67850</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>67850</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>326411</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>310964</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>343219</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>497</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>332469</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>316268</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>346305</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>315482</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>348110</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>70,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>67,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>326411</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>307511</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>342376</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>636104</t>
+          <t>634904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682300</t>
+          <t>681137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>157662</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>140854</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>173109</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>137475</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>123639</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>153676</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>121834</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>154462</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29,25%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>157662</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>141697</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>176562</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>271717</t>
+          <t>272880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>317913</t>
+          <t>319113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>484073</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>484073</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>484073</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>469944</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>469944</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>469944</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>484073</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>484073</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>484073</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>124842</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>114435</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>135124</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>105495</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>95286</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>116252</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>95457</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>116060</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>124842</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>113822</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>135137</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216512</t>
+          <t>214891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246111</t>
+          <t>244183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61477</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51195</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71884</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64436</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53679</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74645</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53871</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74474</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61477</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51182</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>72497</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110139</t>
+          <t>112067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139738</t>
+          <t>141359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186319</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186319</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186319</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169931</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169931</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169931</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186319</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186319</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186319</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>473777</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>515717</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>64,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>716</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>458336</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>497620</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>461458</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>500683</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>472693</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>515355</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>945678</t>
+          <t>945109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1002204</t>
+          <t>1001563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>243966</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>222525</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>264465</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>218659</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>201633</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>240917</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>198570</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>237795</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>31,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>243966</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>222887</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>265549</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>435932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>491817</t>
+          <t>492386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>699253</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36317</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42217</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34836</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26686</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42335</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31586</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>34636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>74072</t>
+          <t>65828</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>57663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84820</t>
+          <t>74079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20415</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14515</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27120</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18466</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10967</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26616</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,64%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>16134</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52095</t>
+          <t>44715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53302</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53302</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53302</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45645</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45645</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115306</t>
+          <t>102378</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115306</t>
+          <t>102378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115306</t>
+          <t>102378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>330978</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>312822</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>350235</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>426</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>326499</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>308559</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>355661</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>67,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>352960</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>330843</t>
+          <t>288142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>372823</t>
+          <t>317224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>679459</t>
+          <t>634725</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>648742</t>
+          <t>609311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713674</t>
+          <t>658677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>142796</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>123539</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>160952</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>130695</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101533</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>148635</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>161662</t>
+          <t>125480</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>112003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183779</t>
+          <t>141085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>292358</t>
+          <t>268277</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>258143</t>
+          <t>244325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323075</t>
+          <t>293691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>473774</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>473774</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>473774</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>457194</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>457194</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>457194</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514622</t>
+          <t>429227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514622</t>
+          <t>429227</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514622</t>
+          <t>429227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>971817</t>
+          <t>903002</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>971817</t>
+          <t>903002</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>971817</t>
+          <t>903002</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>128737</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>119510</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137462</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>108151</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>99006</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>115745</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138177</t>
+          <t>109476</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127288</t>
+          <t>101033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147970</t>
+          <t>118239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>246327</t>
+          <t>238212</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232299</t>
+          <t>225601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258396</t>
+          <t>250661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39682</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30957</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>48909</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>39594</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32000</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>48739</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35379</t>
+          <t>29784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56061</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>84767</t>
+          <t>78229</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72698</t>
+          <t>65780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98795</t>
+          <t>90840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147745</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147745</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147745</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>148023</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>148023</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>148023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>331094</t>
+          <t>316441</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331094</t>
+          <t>316441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>331094</t>
+          <t>316441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>473783</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>630</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>447342</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>496429</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>71,32%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442734</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>504217</t>
+          <t>423999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>554632</t>
+          <t>460413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>965413</t>
+          <t>909859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033705</t>
+          <t>966511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202894</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>180045</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>225142</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>188756</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161813</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>210900</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>28,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>229602</t>
+          <t>180162</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205343</t>
+          <t>162483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255758</t>
+          <t>198897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>418358</t>
+          <t>383056</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384512</t>
+          <t>355310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>452804</t>
+          <t>411962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>658242</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>658242</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>658242</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>622896</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>622896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>622896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1418217</t>
+          <t>1321821</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1418217</t>
+          <t>1321821</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1418217</t>
+          <t>1321821</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
